--- a/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v3.xlsx
+++ b/20260423 V1 FSO Skills Output_CM_added_element_pcs_fs_refined_v3.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stakeholder Viewpoint Elicitation</t>
+          <t>Viewpoint Elicitation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -688,16 +688,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>keep:0, "Stakeholder Viewpoint Elicitation":10</t>
+          <t>keep:0, "Viewpoint Elicitation":5</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -842,7 +842,7 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -982,16 +982,16 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Generation":10</t>
+          <t>keep:0, "Idea Generation":5</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1136,7 +1136,7 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1269,7 +1269,7 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1402,7 +1402,7 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1534,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>keep:0, "Idea Viability Evaluation":10</t>
+          <t>keep:0, "Idea Viability Evaluation":5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:4, "Issue Selection":1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1825,7 +1825,7 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1958,7 +1958,7 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
-          <t>keep:6, "Information Research":4</t>
+          <t>keep:3, "Information Research":2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2090,16 +2090,16 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 3/5: </t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:2, "Solution Presentation":3</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2235,16 +2235,16 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>keep:0, "Solution Refinement":10</t>
+          <t>keep:0, "Solution Refinement":5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2377,7 +2377,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2518,7 +2518,7 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2654,16 +2654,16 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>keep:3, "Discussion Facilitation":7</t>
+          <t>keep:0, "Discussion Facilitation":5</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2805,7 +2805,7 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2935,7 +2935,7 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -3073,7 +3073,7 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -3198,12 +3198,12 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9357142857142857</v>
+        <v>0.95</v>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
-          <t>keep:7, "Improvement Requirements Communication":3</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -3332,16 +3332,16 @@
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>keep:0, "Insight Presentation":10</t>
+          <t>keep:0, "Insight Presentation":5</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -3475,7 +3475,7 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3613,7 +3613,7 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3746,16 +3746,16 @@
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>keep:0, "Policy Drafting":10</t>
+          <t>keep:0, "Policy Drafting":5</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -3888,16 +3888,16 @@
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>keep:0, "Practice Review":10</t>
+          <t>keep:0, "Practice Review":5</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -4035,7 +4035,7 @@
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -4165,7 +4165,7 @@
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -4299,7 +4299,7 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4579,7 +4579,7 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -5079,7 +5079,7 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -5207,16 +5207,16 @@
         <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>keep:0, "Device Configuration":10</t>
+          <t>keep:0, "Device Configuration":5</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -5349,7 +5349,7 @@
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -5494,7 +5494,7 @@
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -5635,7 +5635,7 @@
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Password Strength Creation</t>
+          <t>Password Creation</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5760,15 +5760,19 @@
         </is>
       </c>
       <c r="U40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:0, "Password Creation":5</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -5909,7 +5913,7 @@
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -6041,16 +6045,16 @@
         <v>1</v>
       </c>
       <c r="V42" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>keep:0, "Data Risk Categorisation/Risk Categorisation":10</t>
+          <t>keep:0, "Data Risk Categorisation":5</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -6186,16 +6190,16 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>keep:0, "Physical Security Plan Communication":10</t>
+          <t>keep:0, "Physical Security Plan Communication":5</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -6336,7 +6340,7 @@
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
@@ -6477,7 +6481,7 @@
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -6513,7 +6517,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Security Development Monitoring</t>
+          <t>Security Trend Monitoring</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6606,19 +6610,15 @@
         </is>
       </c>
       <c r="U46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 10/10: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
-          <t>keep:0, "Security Development Monitoring":10</t>
+          <t>keep:4, "Security Development Monitoring":1</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -6759,7 +6759,7 @@
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -7028,7 +7028,7 @@
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -7156,7 +7156,7 @@
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -7284,7 +7284,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -7403,16 +7403,16 @@
         <v>1</v>
       </c>
       <c r="V52" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 7/10: </t>
+          <t xml:space="preserve">consensus 3/5: </t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>keep:3, "Evaluation Documentation":7</t>
+          <t>keep:1, "Evaluation Documentation":3, "Evaluation Documentation Preparation":1</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -7548,7 +7548,7 @@
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:4, "ICT Gap Identification":1</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -7688,7 +7688,7 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7812,7 +7812,7 @@
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -7936,7 +7936,7 @@
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
         <is>
-          <t>keep:8, "Financial Impact Interpretation":2</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -8060,7 +8060,7 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -8184,7 +8184,7 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Risk Assessment Planning</t>
+          <t>Change Difficulty Assessment</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8300,15 +8300,19 @@
         </is>
       </c>
       <c r="U59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W59" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/5: </t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:1, "Change Difficulty Assessment":4</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -8444,7 +8448,7 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -8584,7 +8588,7 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -8708,7 +8712,7 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -8832,7 +8836,7 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -8959,7 +8963,7 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -9086,7 +9090,7 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -9213,7 +9217,7 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -9340,7 +9344,7 @@
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -9467,7 +9471,7 @@
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -9594,7 +9598,7 @@
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -9716,12 +9720,12 @@
         <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>0.9471428571428572</v>
+        <v>0.95</v>
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr">
         <is>
-          <t>keep:7, "IP Legislation Analysis":2, "Intellectual Property Legislation Analysis":1</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -9843,12 +9847,12 @@
         <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>0.945</v>
+        <v>0.95</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -9975,7 +9979,7 @@
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -10102,7 +10106,7 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -10229,7 +10233,7 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -10356,7 +10360,7 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -10483,7 +10487,7 @@
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -10610,7 +10614,7 @@
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -10737,7 +10741,7 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -10871,7 +10875,7 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -11005,7 +11009,7 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
@@ -11139,7 +11143,7 @@
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -11273,7 +11277,7 @@
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
@@ -11407,7 +11411,7 @@
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -11541,7 +11545,7 @@
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -11675,7 +11679,7 @@
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
@@ -11711,7 +11715,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maintenance Schedule Development</t>
+          <t>Maintenance Schedule Planning</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11801,19 +11805,15 @@
         </is>
       </c>
       <c r="U86" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 5/10: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
         <is>
-          <t>keep:1, "Maintenance Schedule Development":5, "Maintenance Schedule Documentation":4</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Maintenance Testing Execution</t>
+          <t>Maintenance Testing</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11939,15 +11939,19 @@
         </is>
       </c>
       <c r="U87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V87" t="n">
-        <v>0.9499999999999998</v>
-      </c>
-      <c r="W87" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>keep:6, "Maintenance Test Management":2, "Maintenance Testing":1, "Maintenance Test Execution":1</t>
+          <t>keep:0, "Maintenance Testing":5</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -12081,7 +12085,7 @@
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -12215,7 +12219,7 @@
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -12349,7 +12353,7 @@
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -12483,7 +12487,7 @@
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -12617,7 +12621,7 @@
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
@@ -12751,7 +12755,7 @@
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
@@ -12883,16 +12887,16 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>keep:0, "Data Log Ingestion":10</t>
+          <t>keep:0, "Data Log Ingestion":5</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -13033,7 +13037,7 @@
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -13170,7 +13174,7 @@
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -13302,16 +13306,16 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 4/5: </t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>keep:9, "Dataset Creation":1</t>
+          <t>keep:1, "Dataset Creation":4</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -13447,16 +13451,16 @@
         <v>1</v>
       </c>
       <c r="V98" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>keep:0, "False Data Detection":10</t>
+          <t>keep:0, "False Data Detection":5</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -13589,7 +13593,7 @@
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -13730,7 +13734,7 @@
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
@@ -13862,16 +13866,16 @@
         <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>keep:0, "Threat Risk Assessment":10</t>
+          <t>keep:0, "Threat Risk Assessment":5</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -14008,7 +14012,7 @@
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
@@ -14145,7 +14149,7 @@
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -14282,7 +14286,7 @@
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -14419,7 +14423,7 @@
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -14455,7 +14459,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Anomaly Detection Troubleshooting</t>
+          <t>Anomaly Detection</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -14542,15 +14546,19 @@
         </is>
       </c>
       <c r="U106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W106" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 4/5: </t>
+        </is>
+      </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>keep:5, "Anomaly Detection":5</t>
+          <t>keep:1, "Anomaly Detection":4</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -14681,7 +14689,7 @@
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -14812,7 +14820,7 @@
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -14943,7 +14951,7 @@
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -15074,7 +15082,7 @@
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -15205,7 +15213,7 @@
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -15336,7 +15344,7 @@
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -15467,7 +15475,7 @@
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -15503,7 +15511,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Critical Infrastructure Protection Analysis</t>
+          <t>Protection Plan Analysis</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -15590,19 +15598,15 @@
         </is>
       </c>
       <c r="U114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 10/10: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr">
         <is>
-          <t>keep:0, "Critical Infrastructure Protection Analysis":10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -15733,7 +15737,7 @@
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -15859,16 +15863,16 @@
         <v>1</v>
       </c>
       <c r="V116" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>keep:0, "Protection Plan Testing":10</t>
+          <t>keep:0, "Protection Plan Testing":5</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -15999,7 +16003,7 @@
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -16035,7 +16039,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Risk Assessment</t>
+          <t>Risk Assessment Evaluation</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -16122,19 +16126,15 @@
         </is>
       </c>
       <c r="U118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V118" t="n">
-        <v>0.9000000000000001</v>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">consensus 10/10: </t>
-        </is>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr">
         <is>
-          <t>keep:0, "Risk Assessment":10</t>
+          <t>keep:4, "Risk Assessment":1</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -16265,7 +16265,7 @@
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -16396,7 +16396,7 @@
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -16537,7 +16537,7 @@
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Feedback Response Management</t>
+          <t>Feedback Management</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -16666,15 +16666,19 @@
         </is>
       </c>
       <c r="U122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W122" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:0, "Feedback Management":5</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -16807,7 +16811,7 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -16843,7 +16847,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Problem Solving in Security</t>
+          <t>Security Anomaly Identification</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -16943,16 +16947,16 @@
         <v>1</v>
       </c>
       <c r="V124" t="n">
-        <v>0.945</v>
+        <v>0.9</v>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>postprocess: spelling/redundancy</t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:0, "Security Anomaly Identification":5</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -17084,16 +17088,16 @@
         <v>1</v>
       </c>
       <c r="V125" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>keep:0, "Security Requirements Documentation":10</t>
+          <t>keep:0, "Security Requirements Documentation":5</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -17230,7 +17234,7 @@
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -17367,7 +17371,7 @@
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -17508,7 +17512,7 @@
       <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -17649,7 +17653,7 @@
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -17782,7 +17786,7 @@
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -17923,7 +17927,7 @@
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -18064,7 +18068,7 @@
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -18201,7 +18205,7 @@
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -18355,7 +18359,7 @@
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -18505,7 +18509,7 @@
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -18541,7 +18545,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Incident Documentation Preparation</t>
+          <t>Incident Documentation</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -18643,15 +18647,19 @@
         </is>
       </c>
       <c r="U136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V136" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W136" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 3/5: </t>
+        </is>
+      </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:2, "Incident Documentation":3</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -18687,7 +18695,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Response Plan Evaluation</t>
+          <t>Incident Response Plan Evaluation</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -18796,16 +18804,16 @@
         <v>1</v>
       </c>
       <c r="V137" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>keep:0, "Response Plan Evaluation":10</t>
+          <t>keep:0, "Incident Response Plan Evaluation":5</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -18955,7 +18963,7 @@
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -19101,7 +19109,7 @@
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -19246,16 +19254,16 @@
         <v>1</v>
       </c>
       <c r="V140" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>keep:0, "Incident Response Training":10</t>
+          <t>keep:0, "Incident Response Training":5</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -19405,7 +19413,7 @@
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -19559,7 +19567,7 @@
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -19713,7 +19721,7 @@
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -19867,7 +19875,7 @@
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y144" t="inlineStr">
@@ -20021,7 +20029,7 @@
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -20164,7 +20172,7 @@
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -20307,7 +20315,7 @@
       <c r="W147" t="inlineStr"/>
       <c r="X147" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -20454,7 +20462,7 @@
       <c r="W148" t="inlineStr"/>
       <c r="X148" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -20597,7 +20605,7 @@
       <c r="W149" t="inlineStr"/>
       <c r="X149" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -20740,7 +20748,7 @@
       <c r="W150" t="inlineStr"/>
       <c r="X150" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -20883,7 +20891,7 @@
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -21021,16 +21029,16 @@
         <v>1</v>
       </c>
       <c r="V152" t="n">
-        <v>0.9000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t xml:space="preserve">consensus 10/10: </t>
+          <t xml:space="preserve">consensus 5/5: </t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>keep:0, "Business Data Analysis/Data Analysis":10</t>
+          <t>keep:0, "Business Data Analysis":5</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -21173,7 +21181,7 @@
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -21320,7 +21328,7 @@
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -21458,12 +21466,12 @@
         <v>0</v>
       </c>
       <c r="V155" t="n">
-        <v>0.9499999999999998</v>
+        <v>0.95</v>
       </c>
       <c r="W155" t="inlineStr"/>
       <c r="X155" t="inlineStr">
         <is>
-          <t>keep:9, "Risk Assessment":1</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -21606,7 +21614,7 @@
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
@@ -21642,7 +21650,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Strategic Planning</t>
+          <t>Priority Planning</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -21741,15 +21749,19 @@
         </is>
       </c>
       <c r="U157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V157" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W157" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">consensus 5/5: </t>
+        </is>
+      </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:0, "Priority Planning":5</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -21892,7 +21904,7 @@
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
@@ -22035,7 +22047,7 @@
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
@@ -22178,7 +22190,7 @@
       <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
-          <t>keep:10</t>
+          <t>keep:5</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
